--- a/data/irvine_tustin_preschools.xlsx
+++ b/data/irvine_tustin_preschools.xlsx
@@ -1042,7 +1042,7 @@
         <v>Home Kids Academy</v>
       </c>
       <c r="C15" t="str">
-        <v>homekidsacademy.com</v>
+        <v>https://www.hkairvine.com</v>
       </c>
       <c r="D15" t="str">
         <v>Contact school</v>
